--- a/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
@@ -665,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -707,7 +708,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>赋能词缀中文名：短词缀，直接描述强化方向（范围扩大 / 双重释放 / 环绕 / 强行追踪 / 贯穿+ / 从天而降）</t>
+          <t>赋能词缀中文名：短词缀，直接描述强化方向（范围扩大 / 双重释放 / 环绕 / 强行追踪 / 弹道贯穿 / 从天而降）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -783,6 +784,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1033,7 +1035,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>贯穿+</t>
+          <t>弹道贯穿</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1149,6 +1151,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1210,6 +1213,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>

--- a/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,19 @@
       <c r="C12" s="5" t="inlineStr">
         <is>
           <t>载荷计入技能树整装载荷</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>v0.9b 修订</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>新增 12 条词缀：传导（弹道跃迁 / 电磁链锁）、结算（临界引爆）、附着（状态催化）、时机（蓄势派生）、热量（热量节流）、状态条（状态凝滞 / 状态传染）、召唤（机群扩编 / 超频狂暴）、暴击（精准校准 / 致命打击）；主表扩至 18 条，Tag 体系扩为 6 组。暴击规则定稿：基础暴击率 0%、暴击倍率 ×3.0；「标记」为技能附着的辅助型状态，仅被引爆时兑现暴击加成（方案 A）。</t>
         </is>
       </c>
     </row>
@@ -665,7 +678,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -708,12 +720,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>赋能词缀中文名：短词缀，直接描述强化方向（范围扩大 / 双重释放 / 环绕 / 强行追踪 / 弹道贯穿 / 从天而降）</t>
+          <t>赋能词缀中文名：短词缀，4 字为主（仅「环绕」2 字），结构＝[方式/领域]＋[动作]，直接描述强化方向</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>范围扩大</t>
+          <t>范围扩大 / 双重释放 / 环绕 / 强行追踪 / 弹道贯穿 / 从天而降 / 弹道跃迁 / 电磁链锁 / 临界引爆 / 状态催化 / 蓄势派生 / 热量节流 / 状态凝滞 / 状态传染 / 机群扩编 / 超频狂暴 / 精准校准 / 致命打击</t>
         </is>
       </c>
     </row>
@@ -730,7 +742,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>EN_RANGE / EN_DOUBLE / EN_ORBIT / EN_HOMING / EN_AP / EN_ASTRA</t>
+          <t>EN_RANGE / EN_DOUBLE / EN_ORBIT / EN_HOMING / EN_AP / EN_ASTRA / EN_RICO / EN_LINK / EN_DETON / EN_CATALYST / EN_CHARGE / EN_THROTTLE / EN_STASIS / EN_CONTAGION / EN_LEGION / EN_FRENZY / EN_PRECISION / EN_LETHAL</t>
         </is>
       </c>
     </row>
@@ -762,17 +774,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
@@ -780,11 +792,10 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>A. 赋能词缀主表（每词缀一行 · 词缀模型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>A. 赋能词缀主表（每词缀一行 · 词缀模型 · 18 条）</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1120,6 +1131,582 @@
         <v>18</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>弹道跃迁</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>EN_RICO</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>弹射</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>命中后伤害向最近未命中目标跳转（跳数 2–3、每跳衰减 −20%）</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>仅限「点命中」类行为卡</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>单点最高伤被摊薄（群怪强、单体弱）；与「从天而降」同卡互斥</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>电磁链锁</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>EN_LINK</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>链接</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>多弹道之间建立电磁链，链上目标持续受传导伤害（链长 2–4、持续 1.5–2s）</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>仅限「多弹道/多发」类行为卡（弹道数 ≥2）</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>需多弹道载体（单弹单发无收益）；与「弹道跃迁」可叠加（建网＋放网）</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>临界引爆</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>EN_DETON</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>引爆</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>命中已附着侵蚀的敌人时，把侵蚀累计值提前结算为爆发并清零（倍率 ×1.8–2.5、结算后冷却 1s）</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>仅限侵蚀类行为卡</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>放弃「满条自动施加」的持续收益换爆发；结算后条清零＋冷却，防连环炸</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>状态催化</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>EN_CATALYST</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>附着</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>命中时按比例加速填充目标状态累计条（+30%–50% 累计速度），不直接施加状态</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>需该卡有对应状态累计渠道</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>只加速不制造（守「状态由他树制造」铁律）；对无状态卡无效</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>蓄势派生</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>EN_CHARGE</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>时机</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>技能可蓄力，越久越强（伤害/范围/累计）；或命中后派生一次追加攻击（派生＝本体 ×40%–60%）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>与「从天而降」同属时机维度，建议互斥；蓄力改变节奏</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>热量节流</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>EN_THROTTLE</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>热量</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>本卡积热 −X%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>纯降积热，不与「机甲核心」的热量规则冲突</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>状态凝滞</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>EN_STASIS</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>凝滞</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>本卡命中时，减缓目标状态条衰减速度（延长状态窗口）</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>与「状态催化」互补（一个加速累计、一个减缓衰减）</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>状态传染</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>EN_CONTAGION</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>传染</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>本卡命中时，把目标部分累计值传染给邻近敌人</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>需邻近有敌人（对单体无收益）</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>机群扩编</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>EN_LEGION</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>扩编</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>召唤物数量上限＋、在场时长＋</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为卡</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>与「超频狂暴」互斥（求稳 vs 求爆）</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>超频狂暴</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>EN_FRENZY</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>狂暴</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>召唤物在场时长 −50%、持续扣血（自伤），换攻速 ×2</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为卡</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>风险收益型；与「机群扩编」互斥</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>精准校准</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>EN_PRECISION</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>精准</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>本卡暴击率 +X%</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>基础暴击率 0%（不投入即无暴击）；受暴击率软上限（75%）约束</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>致命打击</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>EN_LETHAL</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>致命</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>本卡暴击倍率 +X%（基础 ×3.0）</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>与「精准校准」互补（起势 vs 放大）；无暴击率时收益为零</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>新增</t>
         </is>
@@ -1136,12 +1723,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,7 +1738,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1172,7 +1758,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>强化方向</t>
+          <t>命中形态</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -1182,7 +1768,92 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>赋能插件（检索分类；一个词缀归属一个强化方向 Tag；随新词缀设计扩展 Tag 组）</t>
+          <t>描述「怎么打中」——v0.9 原有 6 词缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>传导</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>弹射 / 链接</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>命中后伤害在目标 / 弹道之间扩散（弹射放网、链接建网）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>引爆</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>把已累计的状态提前兑现为爆发</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>状态互动</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>附着 / 凝滞 / 传染</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>与状态累计条互动（加速累计 / 减缓衰减 / 扩散给邻近）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>节奏资源</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>时机 / 热量</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>改变攻击节奏与热量收支</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>专项强化</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>扩编 / 狂暴 / 精准 / 致命</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>强化召唤物（数量 / 时长 / 狂暴）与暴击输出</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1213,7 +1884,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1365,6 +2035,270 @@
       <c r="D9" s="6" t="inlineStr">
         <is>
           <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>弹射</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>仅限「点命中」类行为卡</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>单点最高伤被摊薄；与「从天而降」同卡互斥</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>链接</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>仅限「多弹道/多发」类行为卡（弹道数 ≥2）</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>需多弹道载体；与「弹射」可叠加（建网＋放网）</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>引爆</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>仅限侵蚀类行为卡</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>放弃满条持续收益换爆发；结算后清零＋冷却防连环炸</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>附着</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>需该卡有对应状态累计渠道</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>只加速不制造（守跨树铁律）；对无状态卡无效</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>时机</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>与「从天而降」同属时机维度，建议互斥</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>热量</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>纯降积热，不与「机甲核心」热量规则冲突</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>凝滞</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>与「附着」互补（加速累计 vs 减缓衰减）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>传染</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>需邻近有敌人；对单体无收益</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>扩编</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为卡</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>与「狂暴」互斥（求稳 vs 求爆）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>狂暴</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为卡</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>风险收益型（自伤换攻速）；与「扩编」互斥</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>精准</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>基础暴击率 0%；受软上限约束</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>致命</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>与「精准」互补；无暴击率时收益为零</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
         </is>
       </c>
     </row>

--- a/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>赋能插件 = 行为插件的词缀，不分稀有度、不占槽位、不入树结构：从构装库拖到行为卡上（或点行为卡「◆赋能」选择），作用于所附着的那张行为卡本身（直接子节点）。主表（A）每词缀一行；命名规范页定义命名；Tag体系页定义检索分类；受附要求体系页定义可附着对象与适用性权衡。</t>
+          <t>赋能插件 = 行为插件的词缀，不分稀有度、不占槽位、不入树结构：从构装库拖到行为插件上（或点行为插件「◆赋能」选择），作用于所附着的那个行为插件本身（直接子节点）。主表（A）每词缀一行；命名规范页定义命名；Tag体系页定义检索分类；受附要求体系页定义可附着对象与适用性权衡。</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>行为/中继构成「行为→中继→行为」纯链，行为卡本身占槽入树</t>
+          <t>行为/中继构成「行为→中继→行为」纯链，行为插件本身占槽入树</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>只作用于所附着的那张行为卡本身（直接子节点）</t>
+          <t>只作用于所附着的那个行为插件本身（直接子节点）</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>每张行为卡最多附着 2 个赋能（原型 MAX_AFFIXES=2），载荷叠加到所属卡</t>
+          <t>每个行为插件最多附着 2 个赋能（原型 MAX_AFFIXES=2），载荷叠加到所属插件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>受每卡赋能上限（≤2）与载荷约束</t>
+          <t>受每插件赋能上限（≤2）与载荷约束</t>
         </is>
       </c>
       <c r="I5" s="6" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>仅限远程/弹道类行为卡</t>
+          <t>仅限远程/弹道类行为插件</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>仅限弹道类行为卡</t>
+          <t>仅限弹道类行为插件</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>仅限「点命中」类行为卡</t>
+          <t>仅限「点命中」类行为插件</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>单点最高伤被摊薄（群怪强、单体弱）；与「从天而降」同卡互斥</t>
+          <t>单点最高伤被摊薄（群怪强、单体弱）；与「从天而降」同插件互斥</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>仅限「多弹道/多发」类行为卡（弹道数 ≥2）</t>
+          <t>仅限「多弹道/多发」类行为插件（弹道数 ≥2）</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>仅限侵蚀类行为卡</t>
+          <t>仅限侵蚀类行为插件</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>需该卡有对应状态累计渠道</t>
+          <t>需该插件有对应状态累计渠道</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>只加速不制造（守「状态由他树制造」铁律）；对无状态卡无效</t>
+          <t>只加速不制造（守「状态由他树制造」铁律）；对无状态插件无效</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>本卡积热 −X%</t>
+          <t>本插件积热 −X%</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>本卡命中时，减缓目标状态条衰减速度（延长状态窗口）</t>
+          <t>本插件命中时，减缓目标状态条衰减速度（延长状态窗口）</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>本卡命中时，把目标部分累计值传染给邻近敌人</t>
+          <t>本插件命中时，把目标部分累计值传染给邻近敌人</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>仅限召唤类行为卡</t>
+          <t>仅限召唤类行为插件</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>仅限召唤类行为卡</t>
+          <t>仅限召唤类行为插件</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>本卡暴击率 +X%</t>
+          <t>本插件暴击率 +X%</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>本卡暴击倍率 +X%（基础 ×3.0）</t>
+          <t>本插件暴击倍率 +X%（基础 ×3.0）</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>受每卡赋能上限（≤2）与载荷约束</t>
+          <t>受每插件赋能上限（≤2）与载荷约束</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>仅限弹道类行为卡</t>
+          <t>仅限弹道类行为插件</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>仅限远程/弹道类行为卡；近战不可赋予</t>
+          <t>仅限远程/弹道类行为插件；近战不可赋予</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>仅限「点命中」类行为卡</t>
+          <t>仅限「点命中」类行为插件</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>单点最高伤被摊薄；与「从天而降」同卡互斥</t>
+          <t>单点最高伤被摊薄；与「从天而降」同插件互斥</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>仅限「多弹道/多发」类行为卡（弹道数 ≥2）</t>
+          <t>仅限「多弹道/多发」类行为插件（弹道数 ≥2）</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>仅限侵蚀类行为卡</t>
+          <t>仅限侵蚀类行为插件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>需该卡有对应状态累计渠道</t>
+          <t>需该插件有对应状态累计渠道</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>只加速不制造（守跨树铁律）；对无状态卡无效</t>
+          <t>只加速不制造（守跨树铁律）；对无状态插件无效</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>仅限召唤类行为卡</t>
+          <t>仅限召唤类行为插件</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>仅限召唤类行为卡</t>
+          <t>仅限召唤类行为插件</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">

--- a/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -119,6 +119,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -646,9 +649,22 @@
           <t>v0.9b 修订</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>新增 12 条词缀：传导（弹道跃迁 / 电磁链锁）、结算（临界引爆）、附着（状态催化）、时机（蓄势派生）、热量（热量节流）、状态条（状态凝滞 / 状态传染）、召唤（机群扩编 / 超频狂暴）、暴击（精准校准 / 致命打击）；主表扩至 18 条，Tag 体系扩为 6 组。暴击规则定稿：基础暴击率 0%、暴击倍率 ×3.0；「标记」为技能附着的辅助型状态，仅被引爆时兑现暴击加成（方案 A）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>v0.9c 修订</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>概念定稿（2026-10-01）：触发下游 = 中继专属职责（条件满足才触发，条件苛刻度门控效率）；赋能不做触发，但可做「依据上游改变自身形态」的变形词缀。新增 2 条：散射 EN_SCATTER（3 股霰弹式弹幕，每股 40%，与双重释放互斥）、公转 EN_REVOLVE（所附插件绕上游行为插件运行，与环绕可成日-月双层轨道）；环绕描述拆清为「绕本体自转」。主表 18→20 条。近战专属赋能 3 案（导电斩击/燃尽重斩/压制重锤）讨论稿，未落表。</t>
         </is>
       </c>
     </row>
@@ -672,7 +688,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>赋能词缀命名规范（v0.9）</t>
         </is>
@@ -774,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -790,9 +806,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>A. 赋能词缀主表（每词缀一行 · 词缀模型 · 18 条）</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>A. 赋能词缀主表（每词缀一行 · 词缀模型 · 20 条）</t>
         </is>
       </c>
     </row>
@@ -965,7 +981,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>环绕本体运作</t>
+          <t>技能实体绕发射原点/机甲本体自转一圈（轨道半径固定）；若所附插件为下游且附「公转」，则卫星点再自转（日-月双层轨道）</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -980,7 +996,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>与「强行追踪」（长距索敌）互斥</t>
+          <t>与「强行追踪」（长距索敌）互斥；可与「公转」组成双层轨道</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
@@ -988,7 +1004,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>v0.9c 修订</t>
         </is>
       </c>
     </row>
@@ -1709,6 +1725,102 @@
       <c r="J21" s="6" t="inlineStr">
         <is>
           <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>散射</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>EN_SCATTER</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>散射</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>单次释放分裂为 3 股霰弹式弹幕，横向散布；每股伤害 40%（3×40%=总伤 120%，总伤略升、单点覆盖变宽）；近战形态＝分裂为 3 道扇形斩击弧</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>与「双重释放」互斥（同属多重，两套散布不叠做）；单体最高伤被摊薄；与「电磁链锁」推荐组合（3 股弹道满足链锁载体）</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>v0.9c 新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>公转</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>EN_REVOLVE</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>公转</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>所附插件实体化为卫星，绕「上游行为插件」运转（轨道跟随上游位置）；若同时附「环绕」，卫星点再自转——下游绕上游公转、点上再自转（月球-太阳关系）</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>需为树内下游插件（有上游行为插件；根级/独立运行插件无「上游」，不可附）</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>把下游技能变成常驻轨道体：触发仍由中继决定，但覆盖面/存在感常驻；与「强行追踪」方向冲突建议互斥</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>v0.9c 新增</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1844,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Tag 体系（赋能词缀检索 / 强化方向分类 · 可随设计扩展）</t>
         </is>
@@ -1763,12 +1875,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>范围 / 弹道 / 追踪 / 多重 / 环绕 / 触达</t>
+          <t>范围 / 弹道 / 追踪 / 多重 / 环绕 / 公转 / 触达 / 散射</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>描述「怎么打中」——v0.9 原有 6 词缀</t>
+          <t>描述「怎么打中」——多重=双重释放/散射（互斥）；环绕=绕本体自转，公转=绕上游运转（可双层轨道）</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1878,7 +1990,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>受附要求体系（对应行为插件「稀有度体系」：词的附着约束与权衡）</t>
         </is>
@@ -2007,7 +2119,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>与「强行追踪」互斥</t>
+          <t>与「强行追踪」互斥；可与「公转」组成双层轨道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2019,7 +2131,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>触达</t>
+          <t>散射</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -2029,51 +2141,51 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>改变命中时机（延迟），需择机使用</t>
+          <t>与「双重释放」互斥（同属多重）；单点摊薄；与「电磁链锁」推荐组合</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>质变</t>
+          <t>加强</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>弹射</t>
+          <t>公转</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>仅限「点命中」类行为插件</t>
+          <t>需为树内下游插件（有上游行为插件）</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>单点最高伤被摊薄；与「从天而降」同插件互斥</t>
+          <t>依据上游改变形态；与「强行追踪」建议互斥</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>加强</t>
+          <t>质变</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>链接</t>
+          <t>触达</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>仅限「多弹道/多发」类行为插件（弹道数 ≥2）</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>需多弹道载体；与「弹射」可叠加（建网＋放网）</t>
+          <t>改变命中时机（延迟），需择机使用</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -2085,61 +2197,61 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>引爆</t>
+          <t>弹射</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>仅限侵蚀类行为插件</t>
+          <t>仅限「点命中」类行为插件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>放弃满条持续收益换爆发；结算后清零＋冷却防连环炸</t>
+          <t>单点最高伤被摊薄；与「从天而降」同插件互斥</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>质变</t>
+          <t>加强</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>附着</t>
+          <t>链接</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>需该插件有对应状态累计渠道</t>
+          <t>仅限「多弹道/多发」类行为插件（弹道数 ≥2）</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>只加速不制造（守跨树铁律）；对无状态插件无效</t>
+          <t>需多弹道载体；与「弹射」可叠加（建网＋放网）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>加强</t>
+          <t>质变</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>时机</t>
+          <t>引爆</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>仅限侵蚀类行为插件</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>与「从天而降」同属时机维度，建议互斥</t>
+          <t>放弃满条持续收益换爆发；结算后清零＋冷却防连环炸</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -2151,17 +2263,17 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>热量</t>
+          <t>附着</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>需该插件有对应状态累计渠道</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>纯降积热，不与「机甲核心」热量规则冲突</t>
+          <t>只加速不制造（守跨树铁律）；对无状态插件无效</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2173,7 +2285,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>凝滞</t>
+          <t>时机</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2183,19 +2295,19 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>与「附着」互补（加速累计 vs 减缓衰减）</t>
+          <t>与「从天而降」同属时机维度，建议互斥</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>加强</t>
+          <t>质变</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>传染</t>
+          <t>热量</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -2205,29 +2317,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>需邻近有敌人；对单体无收益</t>
+          <t>纯降积热，不与「机甲核心」热量规则冲突</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>质变</t>
+          <t>加强</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>扩编</t>
+          <t>凝滞</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>仅限召唤类行为插件</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>与「狂暴」互斥（求稳 vs 求爆）</t>
+          <t>与「附着」互补（加速累计 vs 减缓衰减）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2239,17 +2351,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>狂暴</t>
+          <t>传染</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>仅限召唤类行为插件</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>风险收益型（自伤换攻速）；与「扩编」互斥</t>
+          <t>需邻近有敌人；对单体无收益</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2261,17 +2373,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>精准</t>
+          <t>扩编</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>仅限召唤类行为插件</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>基础暴击率 0%；受软上限约束</t>
+          <t>与「狂暴」互斥（求稳 vs 求爆）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2283,20 +2395,64 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t>狂暴</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为插件</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>风险收益型（自伤换攻速）；与「扩编」互斥</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>精准</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>基础暴击率 0%；受软上限约束</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>致命</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>与「精准」互补；无暴击率时收益为零</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>加强</t>
         </is>

--- a/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/enhance-plugin-tables-v0.9.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,18 @@
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>概念定稿（2026-10-01）：触发下游 = 中继专属职责（条件满足才触发，条件苛刻度门控效率）；赋能不做触发，但可做「依据上游改变自身形态」的变形词缀。新增 2 条：散射 EN_SCATTER（3 股霰弹式弹幕，每股 40%，与双重释放互斥）、公转 EN_REVOLVE（所附插件绕上游行为插件运行，与环绕可成日-月双层轨道）；环绕描述拆清为「绕本体自转」。主表 18→20 条。近战专属赋能 3 案（导电斩击/燃尽重斩/压制重锤）讨论稿，未落表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>v0.9d 新增 3 条（2026-10-01）</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>用户拍板的近战三案「去近战化」落地：雷引 EN_CONDUCT（命中感电敌人时 ×1.4 并向身边 2 敌传导 40%，命中点建网，与电磁链锁可叠加）、助燃 EN_STOKE（命中燃烧敌人时燃烧伤害 +30% 并刷新时长 3s，燃烧持续线路，与临界引爆的爆发线互斥——引爆不滥用，两条燃烧路线并行）、断稳 EN_STALL（命中失衡敌人时失衡条衰减暂停 1.5s，踩住控制期与失衡爆破中继联动，与状态催化剂错开：建条 vs 踩条）。主表 20→23 条。</t>
         </is>
       </c>
     </row>
@@ -790,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -808,7 +820,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>A. 赋能词缀主表（每词缀一行 · 词缀模型 · 20 条）</t>
+          <t>A. 赋能词缀主表（每词缀一行 · 词缀模型 · 23 条）</t>
         </is>
       </c>
     </row>
@@ -1821,6 +1833,150 @@
       <c r="J23" s="6" t="inlineStr">
         <is>
           <t>v0.9c 新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>雷引</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>EN_CONDUCT</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>雷引</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>命中处于「感电」状态的敌人时，伤害 ×1.4，并向其身边 2 个敌人传导 40% 伤害（以命中点为载体建网）</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>通用（触发依赖感电目标）</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>无感电目标时零收益（须他树先制造感电，守跨树铁律）；与「电磁链锁」载体不同（弹道建网 vs 命中点建网），可叠加以扩大电网覆盖</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>v0.9d 新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>助燃</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>EN_STOKE</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>助燃</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>命中处于「燃烧」状态的敌人时，其燃烧伤害 +30% 且燃烧时长刷新回 3s（把燃烧做成高频命中维持型 DoT）</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>通用（触发依赖燃烧目标）</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>须先有燃烧（他树/召唤物制造均可）；使燃烧 BD 走「持续线」——与「临界引爆」的爆发线互斥（引爆结算会清空燃烧）</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>v0.9d 新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>断稳</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>EN_STALL</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>断稳</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>命中处于「失衡」控制态的敌人时，其失衡条衰减暂停 1.5s（把约 2s 控制期「踩住」延长）</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>通用（触发依赖失衡目标）</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>与「失衡爆破」中继强联动（拖长控制窗口多喂一轮触发）；对未失衡目标无收益；与「状态催化（失衡）」错开：催化提前建条，断稳踩住现条</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>v0.9d 新增</t>
         </is>
       </c>
     </row>
@@ -1892,12 +2048,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>弹射 / 链接</t>
+          <t>弹射 / 链接 / 雷引</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>命中后伤害在目标 / 弹道之间扩散（弹射放网、链接建网）</t>
+          <t>命中后伤害在目标 / 弹道之间扩散（弹射放网、链接建网、雷引以命中点为载体建网）</t>
         </is>
       </c>
     </row>
@@ -1926,12 +2082,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>附着 / 凝滞 / 传染</t>
+          <t>附着 / 凝滞 / 传染 / 助燃 / 断稳</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>与状态累计条互动（加速累计 / 减缓衰减 / 扩散给邻近）</t>
+          <t>与状态累计条 / 存续状态互动（加速累计 / 减缓衰减 / 传染扩散 / 助燃维持 DoT / 断稳踩住控制期）</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2251,7 +2407,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>放弃满条持续收益换爆发；结算后清零＋冷却防连环炸</t>
+          <t>放弃满条持续收益换爆发；结算后清零＋冷却防连环炸；与「助燃」互斥（爆发线 vs 持续线）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -2263,83 +2419,83 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>附着</t>
+          <t>雷引</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>需该插件有对应状态累计渠道</t>
+          <t>通用（触发依赖感电目标）</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>只加速不制造（守跨树铁律）；对无状态插件无效</t>
+          <t>与「电磁链锁」可叠加（载体不同）；无感电目标零收益</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>加强</t>
+          <t>质变</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>时机</t>
+          <t>助燃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>通用（触发依赖燃烧目标）</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>与「从天而降」同属时机维度，建议互斥</t>
+          <t>与「临界引爆」互斥（燃烧持续线 vs 爆发线）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>质变</t>
+          <t>加强</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>热量</t>
+          <t>断稳</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>通用（触发依赖失衡目标）</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>纯降积热，不与「机甲核心」热量规则冲突</t>
+          <t>与「状态催化（失衡）」错开（建条 vs 踩条）；与「失衡爆破」中继联动</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>加强</t>
+          <t>质变</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>凝滞</t>
+          <t>附着</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>需该插件有对应状态累计渠道</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>与「附着」互补（加速累计 vs 减缓衰减）</t>
+          <t>只加速不制造（守跨树铁律）；对无状态插件无效</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2351,7 +2507,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>传染</t>
+          <t>时机</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -2361,7 +2517,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>需邻近有敌人；对单体无收益</t>
+          <t>与「从天而降」同属时机维度，建议互斥</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -2373,17 +2529,17 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>扩编</t>
+          <t>热量</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>仅限召唤类行为插件</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>与「狂暴」互斥（求稳 vs 求爆）</t>
+          <t>纯降积热，不与「机甲核心」热量规则冲突</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2395,29 +2551,29 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>狂暴</t>
+          <t>凝滞</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>仅限召唤类行为插件</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>风险收益型（自伤换攻速）；与「扩编」互斥</t>
+          <t>与「附着」互补（加速累计 vs 减缓衰减）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>质变</t>
+          <t>加强</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>精准</t>
+          <t>传染</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2427,32 +2583,98 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>基础暴击率 0%；受软上限约束</t>
+          <t>需邻近有敌人；对单体无收益</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>加强</t>
+          <t>质变</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>扩编</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为插件</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>与「狂暴」互斥（求稳 vs 求爆）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>狂暴</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>仅限召唤类行为插件</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>风险收益型（自伤换攻速）；与「扩编」互斥</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>质变</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>精准</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>基础暴击率 0%；受软上限约束</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>致命</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>通用</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>与「精准」互补；无暴击率时收益为零</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>加强</t>
         </is>
